--- a/data/2025/08-brasov/40198-brasov/budget_file.xlsx
+++ b/data/2025/08-brasov/40198-brasov/budget_file.xlsx
@@ -71,13 +71,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -795,9 +796,10 @@
       </c>
     </row>
     <row r="2">
-      <c r="C2" s="2">
-        <f>===== SECTIUNEATOTAL ====== ===============================</f>
-        <v/>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>====== SECTIUNEATOTAL ====== ===============================</t>
+        </is>
       </c>
       <c r="E2" t="n">
         <v>1</v>
@@ -6893,36 +6895,43 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" t="inlineStr">
+      <c r="A162" s="4" t="inlineStr">
         <is>
           <t>65.10.04</t>
         </is>
       </c>
-      <c r="C162" t="inlineStr">
+      <c r="B162" s="4" t="n"/>
+      <c r="C162" s="4" t="inlineStr">
         <is>
           <t>Invatamant secundar</t>
         </is>
       </c>
-      <c r="E162" t="n">
+      <c r="D162" s="4" t="n"/>
+      <c r="E162" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="F162" t="inlineStr">
+      <c r="F162" s="4" t="inlineStr">
         <is>
           <t>expense_functional</t>
         </is>
       </c>
-      <c r="G162" s="3" t="n">
+      <c r="G162" s="5" t="n">
         <v>41</v>
       </c>
-      <c r="H162" s="3" t="n">
+      <c r="H162" s="5" t="n">
         <v>41</v>
       </c>
-      <c r="I162" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J162" t="inlineStr">
-        <is>
-          <t>ocr</t>
+      <c r="I162" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J162" s="4" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="K162" s="4" t="inlineStr">
+        <is>
+          <t>65.10.04 est2028: parent 41,00 != sum(children) 149,00 (1 children); 65.10.04 est2027: parent 41,00 != sum(children) 149,00 (1 children)</t>
         </is>
       </c>
     </row>
@@ -6971,40 +6980,46 @@
         </is>
       </c>
       <c r="G164" s="3" t="n">
-        <v>41</v>
+        <v>149</v>
       </c>
       <c r="H164" s="3" t="n">
-        <v>41</v>
+        <v>149</v>
       </c>
       <c r="I164" s="3" t="n"/>
       <c r="J164" t="inlineStr">
         <is>
-          <t>llm:gemini-3.6-flash</t>
+          <t>ocr</t>
         </is>
       </c>
     </row>
     <row r="165">
-      <c r="C165" s="2" t="inlineStr">
+      <c r="A165" s="4" t="n"/>
+      <c r="B165" s="4" t="n"/>
+      <c r="C165" s="6" t="inlineStr">
         <is>
           <t>Servicii auxiliare pentru educatie</t>
         </is>
       </c>
-      <c r="E165" t="n">
+      <c r="D165" s="4" t="n"/>
+      <c r="E165" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="F165" t="inlineStr"/>
-      <c r="G165" s="3" t="n">
+      <c r="F165" s="4" t="inlineStr"/>
+      <c r="G165" s="5" t="n">
         <v>12726</v>
       </c>
-      <c r="H165" s="3" t="n">
+      <c r="H165" s="5" t="n">
         <v>12767</v>
       </c>
-      <c r="I165" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J165" t="inlineStr">
-        <is>
-          <t>ocr</t>
+      <c r="I165" s="5" t="n"/>
+      <c r="J165" s="4" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="K165" s="4" t="inlineStr">
+        <is>
+          <t>unparseable cell '0.00 0.00' in column credite_angajament</t>
         </is>
       </c>
     </row>
@@ -12451,9 +12466,10 @@
       </c>
     </row>
     <row r="309">
-      <c r="C309" s="2">
-        <f>== SECTIUNEA FUNCTIONARE === ===============================</f>
-        <v/>
+      <c r="C309" s="2" t="inlineStr">
+        <is>
+          <t>=== SECTIUNEA FUNCTIONARE === ===============================</t>
+        </is>
       </c>
       <c r="E309" t="n">
         <v>11</v>
@@ -12679,41 +12695,41 @@
       </c>
     </row>
     <row r="316">
-      <c r="A316" s="6" t="inlineStr">
+      <c r="A316" s="7" t="inlineStr">
         <is>
           <t>33.10.08</t>
         </is>
       </c>
-      <c r="B316" s="6" t="n"/>
-      <c r="C316" s="6" t="inlineStr">
+      <c r="B316" s="7" t="n"/>
+      <c r="C316" s="7" t="inlineStr">
         <is>
           <t>331005+331008+331013+331014+331016+331017+331019+331021+331030la</t>
         </is>
       </c>
-      <c r="D316" s="6" t="n"/>
-      <c r="E316" s="6" t="n">
+      <c r="D316" s="7" t="n"/>
+      <c r="E316" s="7" t="n">
         <v>11</v>
       </c>
-      <c r="F316" s="6" t="inlineStr">
+      <c r="F316" s="7" t="inlineStr">
         <is>
           <t>revenue</t>
         </is>
       </c>
-      <c r="G316" s="7" t="n">
+      <c r="G316" s="8" t="n">
         <v>991</v>
       </c>
-      <c r="H316" s="7" t="n">
+      <c r="H316" s="8" t="n">
         <v>994</v>
       </c>
-      <c r="I316" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J316" s="6" t="inlineStr">
-        <is>
-          <t>ocr</t>
-        </is>
-      </c>
-      <c r="K316" s="6" t="inlineStr">
+      <c r="I316" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J316" s="7" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="K316" s="7" t="inlineStr">
         <is>
           <t>name mismatch vs nomenclator (2%): '331005+331008+331013+331014+331016+33101' vs 'Venituri din prestari de servicii'</t>
         </is>
@@ -13232,45 +13248,45 @@
       </c>
     </row>
     <row r="332">
-      <c r="A332" s="6" t="inlineStr">
+      <c r="A332" s="7" t="inlineStr">
         <is>
           <t>10.01</t>
         </is>
       </c>
-      <c r="B332" s="6" t="inlineStr">
+      <c r="B332" s="7" t="inlineStr">
         <is>
           <t>50.10</t>
         </is>
       </c>
-      <c r="C332" s="6" t="inlineStr">
+      <c r="C332" s="7" t="inlineStr">
         <is>
           <t>Cheltuieli salariale in bani (cod 10.01.01+10.01.03 la 10.01.17+10.01.29+10.01.30)</t>
         </is>
       </c>
-      <c r="D332" s="6" t="n"/>
-      <c r="E332" s="6" t="n">
+      <c r="D332" s="7" t="n"/>
+      <c r="E332" s="7" t="n">
         <v>12</v>
       </c>
-      <c r="F332" s="6" t="inlineStr">
-        <is>
-          <t>expense_economic</t>
-        </is>
-      </c>
-      <c r="G332" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H332" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I332" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J332" s="6" t="inlineStr">
-        <is>
-          <t>ocr</t>
-        </is>
-      </c>
-      <c r="K332" s="6" t="inlineStr">
+      <c r="F332" s="7" t="inlineStr">
+        <is>
+          <t>expense_economic</t>
+        </is>
+      </c>
+      <c r="G332" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H332" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I332" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J332" s="7" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="K332" s="7" t="inlineStr">
         <is>
           <t>duplicate of p12 with different values</t>
         </is>
@@ -23254,352 +23270,352 @@
       </c>
     </row>
     <row r="593">
-      <c r="A593" s="6" t="inlineStr">
+      <c r="A593" s="7" t="inlineStr">
         <is>
           <t>43.10.19</t>
         </is>
       </c>
-      <c r="B593" s="6" t="n"/>
-      <c r="C593" s="6" t="inlineStr">
+      <c r="B593" s="7" t="n"/>
+      <c r="C593" s="7" t="inlineStr">
         <is>
           <t>Subventii pentru institutiile publice destinate sectiunii de dezvoltare</t>
         </is>
       </c>
-      <c r="D593" s="6" t="n"/>
-      <c r="E593" s="6" t="n">
+      <c r="D593" s="7" t="n"/>
+      <c r="E593" s="7" t="n">
         <v>21</v>
       </c>
-      <c r="F593" s="6" t="inlineStr">
+      <c r="F593" s="7" t="inlineStr">
         <is>
           <t>revenue</t>
         </is>
       </c>
-      <c r="G593" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H593" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I593" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J593" s="6" t="inlineStr">
-        <is>
-          <t>ocr</t>
-        </is>
-      </c>
-      <c r="K593" s="6" t="inlineStr">
+      <c r="G593" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H593" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I593" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J593" s="7" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="K593" s="7" t="inlineStr">
         <is>
           <t>duplicate of p2 with different values</t>
         </is>
       </c>
     </row>
     <row r="594">
-      <c r="A594" s="6" t="inlineStr">
+      <c r="A594" s="7" t="inlineStr">
         <is>
           <t>50.10</t>
         </is>
       </c>
-      <c r="B594" s="6" t="n"/>
-      <c r="C594" s="6" t="inlineStr">
+      <c r="B594" s="7" t="n"/>
+      <c r="C594" s="7" t="inlineStr">
         <is>
           <t>CHELTUIELILE SECTIUNII DE DEZVOLTARE (cOd 50.10+59.10+63.10+69.10+79.10)</t>
         </is>
       </c>
-      <c r="D594" s="6" t="n"/>
-      <c r="E594" s="6" t="n">
+      <c r="D594" s="7" t="n"/>
+      <c r="E594" s="7" t="n">
         <v>21</v>
       </c>
-      <c r="F594" s="6" t="inlineStr">
+      <c r="F594" s="7" t="inlineStr">
         <is>
           <t>expense_functional</t>
         </is>
       </c>
-      <c r="G594" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H594" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I594" s="7" t="n">
+      <c r="G594" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H594" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I594" s="8" t="n">
         <v>14343</v>
       </c>
-      <c r="J594" s="6" t="inlineStr">
-        <is>
-          <t>ocr</t>
-        </is>
-      </c>
-      <c r="K594" s="6" t="inlineStr">
+      <c r="J594" s="7" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="K594" s="7" t="inlineStr">
         <is>
           <t>duplicate of p2 with different values</t>
         </is>
       </c>
     </row>
     <row r="595">
-      <c r="A595" s="6" t="inlineStr">
+      <c r="A595" s="7" t="inlineStr">
         <is>
           <t>70</t>
         </is>
       </c>
-      <c r="B595" s="6" t="inlineStr">
+      <c r="B595" s="7" t="inlineStr">
         <is>
           <t>50.10</t>
         </is>
       </c>
-      <c r="C595" s="6" t="inlineStr">
+      <c r="C595" s="7" t="inlineStr">
         <is>
           <t>CHELTUIELI DE CAPITAL</t>
         </is>
       </c>
-      <c r="D595" s="6" t="n"/>
-      <c r="E595" s="6" t="n">
+      <c r="D595" s="7" t="n"/>
+      <c r="E595" s="7" t="n">
         <v>21</v>
       </c>
-      <c r="F595" s="6" t="inlineStr">
-        <is>
-          <t>expense_economic</t>
-        </is>
-      </c>
-      <c r="G595" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H595" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I595" s="7" t="n">
+      <c r="F595" s="7" t="inlineStr">
+        <is>
+          <t>expense_economic</t>
+        </is>
+      </c>
+      <c r="G595" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H595" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I595" s="8" t="n">
         <v>14343</v>
       </c>
-      <c r="J595" s="6" t="inlineStr">
-        <is>
-          <t>ocr</t>
-        </is>
-      </c>
-      <c r="K595" s="6" t="inlineStr">
+      <c r="J595" s="7" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="K595" s="7" t="inlineStr">
         <is>
           <t>duplicate of p4 with different values</t>
         </is>
       </c>
     </row>
     <row r="596">
-      <c r="A596" s="6" t="inlineStr">
+      <c r="A596" s="7" t="inlineStr">
         <is>
           <t>71</t>
         </is>
       </c>
-      <c r="B596" s="6" t="inlineStr">
+      <c r="B596" s="7" t="inlineStr">
         <is>
           <t>50.10</t>
         </is>
       </c>
-      <c r="C596" s="6" t="inlineStr">
+      <c r="C596" s="7" t="inlineStr">
         <is>
           <t>TITLUL XV ACTIVE NEFINANCIARE</t>
         </is>
       </c>
-      <c r="D596" s="6" t="n"/>
-      <c r="E596" s="6" t="n">
+      <c r="D596" s="7" t="n"/>
+      <c r="E596" s="7" t="n">
         <v>21</v>
       </c>
-      <c r="F596" s="6" t="inlineStr">
-        <is>
-          <t>expense_economic</t>
-        </is>
-      </c>
-      <c r="G596" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H596" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I596" s="7" t="n">
+      <c r="F596" s="7" t="inlineStr">
+        <is>
+          <t>expense_economic</t>
+        </is>
+      </c>
+      <c r="G596" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H596" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I596" s="8" t="n">
         <v>14343</v>
       </c>
-      <c r="J596" s="6" t="inlineStr">
-        <is>
-          <t>ocr</t>
-        </is>
-      </c>
-      <c r="K596" s="6" t="inlineStr">
+      <c r="J596" s="7" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="K596" s="7" t="inlineStr">
         <is>
           <t>duplicate of p4 with different values</t>
         </is>
       </c>
     </row>
     <row r="597">
-      <c r="A597" s="6" t="inlineStr">
+      <c r="A597" s="7" t="inlineStr">
         <is>
           <t>71.01</t>
         </is>
       </c>
-      <c r="B597" s="6" t="inlineStr">
+      <c r="B597" s="7" t="inlineStr">
         <is>
           <t>50.10</t>
         </is>
       </c>
-      <c r="C597" s="6" t="inlineStr">
+      <c r="C597" s="7" t="inlineStr">
         <is>
           <t>Active fixe (cod 71.01.01 la 71.01.03+71.01.30)</t>
         </is>
       </c>
-      <c r="D597" s="6" t="n"/>
-      <c r="E597" s="6" t="n">
+      <c r="D597" s="7" t="n"/>
+      <c r="E597" s="7" t="n">
         <v>21</v>
       </c>
-      <c r="F597" s="6" t="inlineStr">
-        <is>
-          <t>expense_economic</t>
-        </is>
-      </c>
-      <c r="G597" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H597" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I597" s="7" t="n">
+      <c r="F597" s="7" t="inlineStr">
+        <is>
+          <t>expense_economic</t>
+        </is>
+      </c>
+      <c r="G597" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H597" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I597" s="8" t="n">
         <v>14343</v>
       </c>
-      <c r="J597" s="6" t="inlineStr">
-        <is>
-          <t>ocr</t>
-        </is>
-      </c>
-      <c r="K597" s="6" t="inlineStr">
+      <c r="J597" s="7" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="K597" s="7" t="inlineStr">
         <is>
           <t>duplicate of p4 with different values</t>
         </is>
       </c>
     </row>
     <row r="598">
-      <c r="A598" s="6" t="inlineStr">
+      <c r="A598" s="7" t="inlineStr">
         <is>
           <t>71.01.01</t>
         </is>
       </c>
-      <c r="B598" s="6" t="inlineStr">
+      <c r="B598" s="7" t="inlineStr">
         <is>
           <t>50.10</t>
         </is>
       </c>
-      <c r="C598" s="6" t="inlineStr">
+      <c r="C598" s="7" t="inlineStr">
         <is>
           <t>Constructii</t>
         </is>
       </c>
-      <c r="D598" s="6" t="n"/>
-      <c r="E598" s="6" t="n">
+      <c r="D598" s="7" t="n"/>
+      <c r="E598" s="7" t="n">
         <v>21</v>
       </c>
-      <c r="F598" s="6" t="inlineStr">
-        <is>
-          <t>expense_economic</t>
-        </is>
-      </c>
-      <c r="G598" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H598" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I598" s="7" t="n">
+      <c r="F598" s="7" t="inlineStr">
+        <is>
+          <t>expense_economic</t>
+        </is>
+      </c>
+      <c r="G598" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H598" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I598" s="8" t="n">
         <v>11914</v>
       </c>
-      <c r="J598" s="6" t="inlineStr">
-        <is>
-          <t>ocr</t>
-        </is>
-      </c>
-      <c r="K598" s="6" t="inlineStr">
+      <c r="J598" s="7" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="K598" s="7" t="inlineStr">
         <is>
           <t>duplicate of p4 with different values</t>
         </is>
       </c>
     </row>
     <row r="599">
-      <c r="A599" s="6" t="inlineStr">
+      <c r="A599" s="7" t="inlineStr">
         <is>
           <t>71.01.02</t>
         </is>
       </c>
-      <c r="B599" s="6" t="inlineStr">
+      <c r="B599" s="7" t="inlineStr">
         <is>
           <t>50.10</t>
         </is>
       </c>
-      <c r="C599" s="6" t="inlineStr">
+      <c r="C599" s="7" t="inlineStr">
         <is>
           <t>Masini, echipamente si mijloace de transport</t>
         </is>
       </c>
-      <c r="D599" s="6" t="n"/>
-      <c r="E599" s="6" t="n">
+      <c r="D599" s="7" t="n"/>
+      <c r="E599" s="7" t="n">
         <v>21</v>
       </c>
-      <c r="F599" s="6" t="inlineStr">
-        <is>
-          <t>expense_economic</t>
-        </is>
-      </c>
-      <c r="G599" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H599" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I599" s="7" t="n">
+      <c r="F599" s="7" t="inlineStr">
+        <is>
+          <t>expense_economic</t>
+        </is>
+      </c>
+      <c r="G599" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H599" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I599" s="8" t="n">
         <v>2370</v>
       </c>
-      <c r="J599" s="6" t="inlineStr">
-        <is>
-          <t>ocr</t>
-        </is>
-      </c>
-      <c r="K599" s="6" t="inlineStr">
+      <c r="J599" s="7" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="K599" s="7" t="inlineStr">
         <is>
           <t>duplicate of p4 with different values</t>
         </is>
       </c>
     </row>
     <row r="600">
-      <c r="A600" s="6" t="inlineStr">
+      <c r="A600" s="7" t="inlineStr">
         <is>
           <t>71.01.30</t>
         </is>
       </c>
-      <c r="B600" s="6" t="inlineStr">
+      <c r="B600" s="7" t="inlineStr">
         <is>
           <t>50.10</t>
         </is>
       </c>
-      <c r="C600" s="6" t="inlineStr">
+      <c r="C600" s="7" t="inlineStr">
         <is>
           <t>Alte active fixe</t>
         </is>
       </c>
-      <c r="D600" s="6" t="n"/>
-      <c r="E600" s="6" t="n">
+      <c r="D600" s="7" t="n"/>
+      <c r="E600" s="7" t="n">
         <v>21</v>
       </c>
-      <c r="F600" s="6" t="inlineStr">
-        <is>
-          <t>expense_economic</t>
-        </is>
-      </c>
-      <c r="G600" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H600" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I600" s="7" t="n">
+      <c r="F600" s="7" t="inlineStr">
+        <is>
+          <t>expense_economic</t>
+        </is>
+      </c>
+      <c r="G600" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H600" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I600" s="8" t="n">
         <v>59</v>
       </c>
-      <c r="J600" s="6" t="inlineStr">
-        <is>
-          <t>ocr</t>
-        </is>
-      </c>
-      <c r="K600" s="6" t="inlineStr">
+      <c r="J600" s="7" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="K600" s="7" t="inlineStr">
         <is>
           <t>duplicate of p4 with different values</t>
         </is>
@@ -23631,221 +23647,221 @@
       </c>
     </row>
     <row r="602">
-      <c r="A602" s="6" t="inlineStr">
+      <c r="A602" s="7" t="inlineStr">
         <is>
           <t>54.10</t>
         </is>
       </c>
-      <c r="B602" s="6" t="n"/>
-      <c r="C602" s="6" t="inlineStr">
+      <c r="B602" s="7" t="n"/>
+      <c r="C602" s="7" t="inlineStr">
         <is>
           <t>CAP. Alte servicii publice generale</t>
         </is>
       </c>
-      <c r="D602" s="6" t="n"/>
-      <c r="E602" s="6" t="n">
+      <c r="D602" s="7" t="n"/>
+      <c r="E602" s="7" t="n">
         <v>21</v>
       </c>
-      <c r="F602" s="6" t="inlineStr">
+      <c r="F602" s="7" t="inlineStr">
         <is>
           <t>expense_functional</t>
         </is>
       </c>
-      <c r="G602" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H602" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I602" s="7" t="n">
+      <c r="G602" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H602" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I602" s="8" t="n">
         <v>200</v>
       </c>
-      <c r="J602" s="6" t="inlineStr">
-        <is>
-          <t>ocr</t>
-        </is>
-      </c>
-      <c r="K602" s="6" t="inlineStr">
+      <c r="J602" s="7" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="K602" s="7" t="inlineStr">
         <is>
           <t>duplicate of p4 with different values</t>
         </is>
       </c>
     </row>
     <row r="603">
-      <c r="A603" s="6" t="inlineStr">
+      <c r="A603" s="7" t="inlineStr">
         <is>
           <t>70</t>
         </is>
       </c>
-      <c r="B603" s="6" t="inlineStr">
+      <c r="B603" s="7" t="inlineStr">
         <is>
           <t>54.10</t>
         </is>
       </c>
-      <c r="C603" s="6" t="inlineStr">
+      <c r="C603" s="7" t="inlineStr">
         <is>
           <t>CHELTUIELI DE CAPITAL</t>
         </is>
       </c>
-      <c r="D603" s="6" t="n"/>
-      <c r="E603" s="6" t="n">
+      <c r="D603" s="7" t="n"/>
+      <c r="E603" s="7" t="n">
         <v>21</v>
       </c>
-      <c r="F603" s="6" t="inlineStr">
-        <is>
-          <t>expense_economic</t>
-        </is>
-      </c>
-      <c r="G603" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H603" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I603" s="7" t="n">
+      <c r="F603" s="7" t="inlineStr">
+        <is>
+          <t>expense_economic</t>
+        </is>
+      </c>
+      <c r="G603" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H603" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I603" s="8" t="n">
         <v>200</v>
       </c>
-      <c r="J603" s="6" t="inlineStr">
-        <is>
-          <t>ocr</t>
-        </is>
-      </c>
-      <c r="K603" s="6" t="inlineStr">
+      <c r="J603" s="7" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="K603" s="7" t="inlineStr">
         <is>
           <t>duplicate of p5 with different values</t>
         </is>
       </c>
     </row>
     <row r="604">
-      <c r="A604" s="6" t="inlineStr">
+      <c r="A604" s="7" t="inlineStr">
         <is>
           <t>71</t>
         </is>
       </c>
-      <c r="B604" s="6" t="inlineStr">
+      <c r="B604" s="7" t="inlineStr">
         <is>
           <t>54.10</t>
         </is>
       </c>
-      <c r="C604" s="6" t="inlineStr">
+      <c r="C604" s="7" t="inlineStr">
         <is>
           <t>TITLUL XV ACTIVE NEFINANCIARE</t>
         </is>
       </c>
-      <c r="D604" s="6" t="n"/>
-      <c r="E604" s="6" t="n">
+      <c r="D604" s="7" t="n"/>
+      <c r="E604" s="7" t="n">
         <v>21</v>
       </c>
-      <c r="F604" s="6" t="inlineStr">
-        <is>
-          <t>expense_economic</t>
-        </is>
-      </c>
-      <c r="G604" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H604" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I604" s="7" t="n">
+      <c r="F604" s="7" t="inlineStr">
+        <is>
+          <t>expense_economic</t>
+        </is>
+      </c>
+      <c r="G604" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H604" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I604" s="8" t="n">
         <v>200</v>
       </c>
-      <c r="J604" s="6" t="inlineStr">
-        <is>
-          <t>ocr</t>
-        </is>
-      </c>
-      <c r="K604" s="6" t="inlineStr">
+      <c r="J604" s="7" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="K604" s="7" t="inlineStr">
         <is>
           <t>duplicate of p5 with different values</t>
         </is>
       </c>
     </row>
     <row r="605">
-      <c r="A605" s="6" t="inlineStr">
+      <c r="A605" s="7" t="inlineStr">
         <is>
           <t>71.01</t>
         </is>
       </c>
-      <c r="B605" s="6" t="inlineStr">
+      <c r="B605" s="7" t="inlineStr">
         <is>
           <t>54.10</t>
         </is>
       </c>
-      <c r="C605" s="6" t="inlineStr">
+      <c r="C605" s="7" t="inlineStr">
         <is>
           <t>Active fixe (cod 71.01.01 la 71.01.03+71.01.30)</t>
         </is>
       </c>
-      <c r="D605" s="6" t="n"/>
-      <c r="E605" s="6" t="n">
+      <c r="D605" s="7" t="n"/>
+      <c r="E605" s="7" t="n">
         <v>21</v>
       </c>
-      <c r="F605" s="6" t="inlineStr">
-        <is>
-          <t>expense_economic</t>
-        </is>
-      </c>
-      <c r="G605" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H605" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I605" s="7" t="n">
+      <c r="F605" s="7" t="inlineStr">
+        <is>
+          <t>expense_economic</t>
+        </is>
+      </c>
+      <c r="G605" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H605" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I605" s="8" t="n">
         <v>200</v>
       </c>
-      <c r="J605" s="6" t="inlineStr">
-        <is>
-          <t>ocr</t>
-        </is>
-      </c>
-      <c r="K605" s="6" t="inlineStr">
+      <c r="J605" s="7" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="K605" s="7" t="inlineStr">
         <is>
           <t>duplicate of p5 with different values</t>
         </is>
       </c>
     </row>
     <row r="606">
-      <c r="A606" s="6" t="inlineStr">
+      <c r="A606" s="7" t="inlineStr">
         <is>
           <t>71.01.02</t>
         </is>
       </c>
-      <c r="B606" s="6" t="inlineStr">
+      <c r="B606" s="7" t="inlineStr">
         <is>
           <t>54.10</t>
         </is>
       </c>
-      <c r="C606" s="6" t="inlineStr">
+      <c r="C606" s="7" t="inlineStr">
         <is>
           <t>Masini, echipamente si mijloace de transport</t>
         </is>
       </c>
-      <c r="D606" s="6" t="n"/>
-      <c r="E606" s="6" t="n">
+      <c r="D606" s="7" t="n"/>
+      <c r="E606" s="7" t="n">
         <v>21</v>
       </c>
-      <c r="F606" s="6" t="inlineStr">
-        <is>
-          <t>expense_economic</t>
-        </is>
-      </c>
-      <c r="G606" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H606" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I606" s="7" t="n">
+      <c r="F606" s="7" t="inlineStr">
+        <is>
+          <t>expense_economic</t>
+        </is>
+      </c>
+      <c r="G606" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H606" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I606" s="8" t="n">
         <v>200</v>
       </c>
-      <c r="J606" s="6" t="inlineStr">
-        <is>
-          <t>ocr</t>
-        </is>
-      </c>
-      <c r="K606" s="6" t="inlineStr">
+      <c r="J606" s="7" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="K606" s="7" t="inlineStr">
         <is>
           <t>duplicate of p5 with different values</t>
         </is>
@@ -23877,299 +23893,299 @@
       </c>
     </row>
     <row r="608">
-      <c r="A608" s="6" t="inlineStr">
+      <c r="A608" s="7" t="inlineStr">
         <is>
           <t>54.10.10</t>
         </is>
       </c>
-      <c r="B608" s="6" t="n"/>
-      <c r="C608" s="6" t="inlineStr">
+      <c r="B608" s="7" t="n"/>
+      <c r="C608" s="7" t="inlineStr">
         <is>
           <t>Servicii publice comunitare de evidenta a persoanelor</t>
         </is>
       </c>
-      <c r="D608" s="6" t="n"/>
-      <c r="E608" s="6" t="n">
+      <c r="D608" s="7" t="n"/>
+      <c r="E608" s="7" t="n">
         <v>21</v>
       </c>
-      <c r="F608" s="6" t="inlineStr">
+      <c r="F608" s="7" t="inlineStr">
         <is>
           <t>expense_functional</t>
         </is>
       </c>
-      <c r="G608" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H608" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I608" s="7" t="n">
+      <c r="G608" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H608" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I608" s="8" t="n">
         <v>200</v>
       </c>
-      <c r="J608" s="6" t="inlineStr">
-        <is>
-          <t>ocr</t>
-        </is>
-      </c>
-      <c r="K608" s="6" t="inlineStr">
+      <c r="J608" s="7" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="K608" s="7" t="inlineStr">
         <is>
           <t>duplicate of p5 with different values</t>
         </is>
       </c>
     </row>
     <row r="609">
-      <c r="A609" s="6" t="inlineStr">
+      <c r="A609" s="7" t="inlineStr">
         <is>
           <t>59.10</t>
         </is>
       </c>
-      <c r="B609" s="6" t="n"/>
-      <c r="C609" s="6" t="inlineStr">
+      <c r="B609" s="7" t="n"/>
+      <c r="C609" s="7" t="inlineStr">
         <is>
           <t>Partea a II-a APARARE,ORDINE PUBLICA SI SIGURANTA NATIONALA</t>
         </is>
       </c>
-      <c r="D609" s="6" t="n"/>
-      <c r="E609" s="6" t="n">
+      <c r="D609" s="7" t="n"/>
+      <c r="E609" s="7" t="n">
         <v>21</v>
       </c>
-      <c r="F609" s="6" t="inlineStr">
+      <c r="F609" s="7" t="inlineStr">
         <is>
           <t>expense_functional</t>
         </is>
       </c>
-      <c r="G609" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H609" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I609" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J609" s="6" t="inlineStr">
-        <is>
-          <t>ocr</t>
-        </is>
-      </c>
-      <c r="K609" s="6" t="inlineStr">
+      <c r="G609" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H609" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I609" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J609" s="7" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="K609" s="7" t="inlineStr">
         <is>
           <t>duplicate of p5 with different values</t>
         </is>
       </c>
     </row>
     <row r="610">
-      <c r="A610" s="6" t="inlineStr">
+      <c r="A610" s="7" t="inlineStr">
         <is>
           <t>63.10</t>
         </is>
       </c>
-      <c r="B610" s="6" t="n"/>
-      <c r="C610" s="6" t="inlineStr">
+      <c r="B610" s="7" t="n"/>
+      <c r="C610" s="7" t="inlineStr">
         <is>
           <t>Partea a IIIl-a CHELTUIELI SOCIAL-CULTURALE</t>
         </is>
       </c>
-      <c r="D610" s="6" t="n"/>
-      <c r="E610" s="6" t="n">
+      <c r="D610" s="7" t="n"/>
+      <c r="E610" s="7" t="n">
         <v>21</v>
       </c>
-      <c r="F610" s="6" t="inlineStr">
+      <c r="F610" s="7" t="inlineStr">
         <is>
           <t>expense_functional</t>
         </is>
       </c>
-      <c r="G610" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H610" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I610" s="7" t="n">
+      <c r="G610" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H610" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I610" s="8" t="n">
         <v>1795</v>
       </c>
-      <c r="J610" s="6" t="inlineStr">
-        <is>
-          <t>ocr</t>
-        </is>
-      </c>
-      <c r="K610" s="6" t="inlineStr">
+      <c r="J610" s="7" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="K610" s="7" t="inlineStr">
         <is>
           <t>duplicate of p5 with different values</t>
         </is>
       </c>
     </row>
     <row r="611">
-      <c r="A611" s="6" t="inlineStr">
+      <c r="A611" s="7" t="inlineStr">
         <is>
           <t>67.10</t>
         </is>
       </c>
-      <c r="B611" s="6" t="n"/>
-      <c r="C611" s="6" t="inlineStr">
+      <c r="B611" s="7" t="n"/>
+      <c r="C611" s="7" t="inlineStr">
         <is>
           <t>CAP. Cultura, recreere si religie</t>
         </is>
       </c>
-      <c r="D611" s="6" t="n"/>
-      <c r="E611" s="6" t="n">
+      <c r="D611" s="7" t="n"/>
+      <c r="E611" s="7" t="n">
         <v>21</v>
       </c>
-      <c r="F611" s="6" t="inlineStr">
+      <c r="F611" s="7" t="inlineStr">
         <is>
           <t>expense_functional</t>
         </is>
       </c>
-      <c r="G611" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H611" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I611" s="7" t="n">
+      <c r="G611" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H611" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I611" s="8" t="n">
         <v>1795</v>
       </c>
-      <c r="J611" s="6" t="inlineStr">
-        <is>
-          <t>ocr</t>
-        </is>
-      </c>
-      <c r="K611" s="6" t="inlineStr">
+      <c r="J611" s="7" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="K611" s="7" t="inlineStr">
         <is>
           <t>duplicate of p6 with different values</t>
         </is>
       </c>
     </row>
     <row r="612">
-      <c r="A612" s="6" t="inlineStr">
+      <c r="A612" s="7" t="inlineStr">
         <is>
           <t>70</t>
         </is>
       </c>
-      <c r="B612" s="6" t="inlineStr">
+      <c r="B612" s="7" t="inlineStr">
         <is>
           <t>67.10</t>
         </is>
       </c>
-      <c r="C612" s="6" t="inlineStr">
+      <c r="C612" s="7" t="inlineStr">
         <is>
           <t>CHELTUIELI DE CAPITAL</t>
         </is>
       </c>
-      <c r="D612" s="6" t="n"/>
-      <c r="E612" s="6" t="n">
+      <c r="D612" s="7" t="n"/>
+      <c r="E612" s="7" t="n">
         <v>21</v>
       </c>
-      <c r="F612" s="6" t="inlineStr">
-        <is>
-          <t>expense_economic</t>
-        </is>
-      </c>
-      <c r="G612" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H612" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I612" s="7" t="n">
+      <c r="F612" s="7" t="inlineStr">
+        <is>
+          <t>expense_economic</t>
+        </is>
+      </c>
+      <c r="G612" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H612" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I612" s="8" t="n">
         <v>1795</v>
       </c>
-      <c r="J612" s="6" t="inlineStr">
-        <is>
-          <t>ocr</t>
-        </is>
-      </c>
-      <c r="K612" s="6" t="inlineStr">
+      <c r="J612" s="7" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="K612" s="7" t="inlineStr">
         <is>
           <t>duplicate of p8 with different values</t>
         </is>
       </c>
     </row>
     <row r="613">
-      <c r="A613" s="6" t="inlineStr">
+      <c r="A613" s="7" t="inlineStr">
         <is>
           <t>71</t>
         </is>
       </c>
-      <c r="B613" s="6" t="inlineStr">
+      <c r="B613" s="7" t="inlineStr">
         <is>
           <t>67.10</t>
         </is>
       </c>
-      <c r="C613" s="6" t="inlineStr">
+      <c r="C613" s="7" t="inlineStr">
         <is>
           <t>TITLUL XV ACTIVE NEFINANCIARE</t>
         </is>
       </c>
-      <c r="D613" s="6" t="n"/>
-      <c r="E613" s="6" t="n">
+      <c r="D613" s="7" t="n"/>
+      <c r="E613" s="7" t="n">
         <v>21</v>
       </c>
-      <c r="F613" s="6" t="inlineStr">
-        <is>
-          <t>expense_economic</t>
-        </is>
-      </c>
-      <c r="G613" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H613" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I613" s="7" t="n">
+      <c r="F613" s="7" t="inlineStr">
+        <is>
+          <t>expense_economic</t>
+        </is>
+      </c>
+      <c r="G613" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H613" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I613" s="8" t="n">
         <v>1795</v>
       </c>
-      <c r="J613" s="6" t="inlineStr">
-        <is>
-          <t>ocr</t>
-        </is>
-      </c>
-      <c r="K613" s="6" t="inlineStr">
+      <c r="J613" s="7" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="K613" s="7" t="inlineStr">
         <is>
           <t>duplicate of p8 with different values</t>
         </is>
       </c>
     </row>
     <row r="614">
-      <c r="A614" s="6" t="inlineStr">
+      <c r="A614" s="7" t="inlineStr">
         <is>
           <t>71.01</t>
         </is>
       </c>
-      <c r="B614" s="6" t="inlineStr">
+      <c r="B614" s="7" t="inlineStr">
         <is>
           <t>67.10</t>
         </is>
       </c>
-      <c r="C614" s="6" t="inlineStr">
+      <c r="C614" s="7" t="inlineStr">
         <is>
           <t>Active fixe (cod 71.01.01 la 71.01.03+71.01.30)</t>
         </is>
       </c>
-      <c r="D614" s="6" t="n"/>
-      <c r="E614" s="6" t="n">
+      <c r="D614" s="7" t="n"/>
+      <c r="E614" s="7" t="n">
         <v>21</v>
       </c>
-      <c r="F614" s="6" t="inlineStr">
-        <is>
-          <t>expense_economic</t>
-        </is>
-      </c>
-      <c r="G614" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H614" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I614" s="7" t="n">
+      <c r="F614" s="7" t="inlineStr">
+        <is>
+          <t>expense_economic</t>
+        </is>
+      </c>
+      <c r="G614" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H614" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I614" s="8" t="n">
         <v>1795</v>
       </c>
-      <c r="J614" s="6" t="inlineStr">
-        <is>
-          <t>ocr</t>
-        </is>
-      </c>
-      <c r="K614" s="6" t="inlineStr">
+      <c r="J614" s="7" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="K614" s="7" t="inlineStr">
         <is>
           <t>duplicate of p8 with different values</t>
         </is>
@@ -24198,123 +24214,123 @@
       </c>
     </row>
     <row r="616">
-      <c r="A616" s="6" t="inlineStr">
+      <c r="A616" s="7" t="inlineStr">
         <is>
           <t>67.10.03</t>
         </is>
       </c>
-      <c r="B616" s="6" t="n"/>
-      <c r="C616" s="6" t="inlineStr">
+      <c r="B616" s="7" t="n"/>
+      <c r="C616" s="7" t="inlineStr">
         <is>
           <t>Din total capitol 67: Servicii culturale</t>
         </is>
       </c>
-      <c r="D616" s="6" t="n">
+      <c r="D616" s="7" t="n">
         <v>1455</v>
       </c>
-      <c r="E616" s="6" t="n">
+      <c r="E616" s="7" t="n">
         <v>22</v>
       </c>
-      <c r="F616" s="6" t="inlineStr">
+      <c r="F616" s="7" t="inlineStr">
         <is>
           <t>expense_functional</t>
         </is>
       </c>
-      <c r="G616" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H616" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I616" s="7" t="n"/>
-      <c r="J616" s="6" t="inlineStr">
-        <is>
-          <t>digital</t>
-        </is>
-      </c>
-      <c r="K616" s="6" t="inlineStr">
+      <c r="G616" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H616" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I616" s="8" t="n"/>
+      <c r="J616" s="7" t="inlineStr">
+        <is>
+          <t>digital</t>
+        </is>
+      </c>
+      <c r="K616" s="7" t="inlineStr">
         <is>
           <t>duplicate of p9 with different values</t>
         </is>
       </c>
     </row>
     <row r="617">
-      <c r="A617" s="6" t="inlineStr">
+      <c r="A617" s="7" t="inlineStr">
         <is>
           <t>67.10.03.04</t>
         </is>
       </c>
-      <c r="B617" s="6" t="n"/>
-      <c r="C617" s="6" t="inlineStr">
+      <c r="B617" s="7" t="n"/>
+      <c r="C617" s="7" t="inlineStr">
         <is>
           <t>Institutii publice de spectacole si concerte</t>
         </is>
       </c>
-      <c r="D617" s="6" t="n">
+      <c r="D617" s="7" t="n">
         <v>1457</v>
       </c>
-      <c r="E617" s="6" t="n">
+      <c r="E617" s="7" t="n">
         <v>22</v>
       </c>
-      <c r="F617" s="6" t="inlineStr">
+      <c r="F617" s="7" t="inlineStr">
         <is>
           <t>expense_functional</t>
         </is>
       </c>
-      <c r="G617" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H617" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I617" s="7" t="n"/>
-      <c r="J617" s="6" t="inlineStr">
-        <is>
-          <t>digital</t>
-        </is>
-      </c>
-      <c r="K617" s="6" t="inlineStr">
+      <c r="G617" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H617" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I617" s="8" t="n"/>
+      <c r="J617" s="7" t="inlineStr">
+        <is>
+          <t>digital</t>
+        </is>
+      </c>
+      <c r="K617" s="7" t="inlineStr">
         <is>
           <t>duplicate of p9 with different values</t>
         </is>
       </c>
     </row>
     <row r="618">
-      <c r="A618" s="6" t="inlineStr">
+      <c r="A618" s="7" t="inlineStr">
         <is>
           <t>67.10.03.30</t>
         </is>
       </c>
-      <c r="B618" s="6" t="n"/>
-      <c r="C618" s="6" t="inlineStr">
+      <c r="B618" s="7" t="n"/>
+      <c r="C618" s="7" t="inlineStr">
         <is>
           <t>Alte servicii culturale</t>
         </is>
       </c>
-      <c r="D618" s="6" t="n">
+      <c r="D618" s="7" t="n">
         <v>1467</v>
       </c>
-      <c r="E618" s="6" t="n">
+      <c r="E618" s="7" t="n">
         <v>22</v>
       </c>
-      <c r="F618" s="6" t="inlineStr">
+      <c r="F618" s="7" t="inlineStr">
         <is>
           <t>expense_functional</t>
         </is>
       </c>
-      <c r="G618" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H618" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I618" s="7" t="n"/>
-      <c r="J618" s="6" t="inlineStr">
-        <is>
-          <t>digital</t>
-        </is>
-      </c>
-      <c r="K618" s="6" t="inlineStr">
+      <c r="G618" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H618" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I618" s="8" t="n"/>
+      <c r="J618" s="7" t="inlineStr">
+        <is>
+          <t>digital</t>
+        </is>
+      </c>
+      <c r="K618" s="7" t="inlineStr">
         <is>
           <t>duplicate of p9 with different values</t>
         </is>
@@ -24356,82 +24372,82 @@
       </c>
     </row>
     <row r="620">
-      <c r="A620" s="6" t="inlineStr">
+      <c r="A620" s="7" t="inlineStr">
         <is>
           <t>79.10</t>
         </is>
       </c>
-      <c r="B620" s="6" t="n"/>
-      <c r="C620" s="6" t="inlineStr">
+      <c r="B620" s="7" t="n"/>
+      <c r="C620" s="7" t="inlineStr">
         <is>
           <t>APE Partea a V-a ACTIUNI ECONOMICE</t>
         </is>
       </c>
-      <c r="D620" s="6" t="n">
+      <c r="D620" s="7" t="n">
         <v>1538</v>
       </c>
-      <c r="E620" s="6" t="n">
+      <c r="E620" s="7" t="n">
         <v>22</v>
       </c>
-      <c r="F620" s="6" t="inlineStr">
+      <c r="F620" s="7" t="inlineStr">
         <is>
           <t>expense_functional</t>
         </is>
       </c>
-      <c r="G620" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H620" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I620" s="7" t="n"/>
-      <c r="J620" s="6" t="inlineStr">
-        <is>
-          <t>digital</t>
-        </is>
-      </c>
-      <c r="K620" s="6" t="inlineStr">
+      <c r="G620" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H620" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I620" s="8" t="n"/>
+      <c r="J620" s="7" t="inlineStr">
+        <is>
+          <t>digital</t>
+        </is>
+      </c>
+      <c r="K620" s="7" t="inlineStr">
         <is>
           <t>duplicate of p9 with different values</t>
         </is>
       </c>
     </row>
     <row r="621">
-      <c r="A621" s="6" t="inlineStr">
+      <c r="A621" s="7" t="inlineStr">
         <is>
           <t>80.10</t>
         </is>
       </c>
-      <c r="B621" s="6" t="n"/>
-      <c r="C621" s="6" t="inlineStr">
+      <c r="B621" s="7" t="n"/>
+      <c r="C621" s="7" t="inlineStr">
         <is>
           <t>CAP. Actiuni generale economice, comerciale si de munca</t>
         </is>
       </c>
-      <c r="D621" s="6" t="n">
+      <c r="D621" s="7" t="n">
         <v>1539</v>
       </c>
-      <c r="E621" s="6" t="n">
+      <c r="E621" s="7" t="n">
         <v>22</v>
       </c>
-      <c r="F621" s="6" t="inlineStr">
+      <c r="F621" s="7" t="inlineStr">
         <is>
           <t>expense_functional</t>
         </is>
       </c>
-      <c r="G621" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H621" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I621" s="7" t="n"/>
-      <c r="J621" s="6" t="inlineStr">
-        <is>
-          <t>digital</t>
-        </is>
-      </c>
-      <c r="K621" s="6" t="inlineStr">
+      <c r="G621" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H621" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I621" s="8" t="n"/>
+      <c r="J621" s="7" t="inlineStr">
+        <is>
+          <t>digital</t>
+        </is>
+      </c>
+      <c r="K621" s="7" t="inlineStr">
         <is>
           <t>duplicate of p9 with different values</t>
         </is>
@@ -24700,303 +24716,303 @@
       </c>
     </row>
     <row r="629">
-      <c r="A629" s="6" t="inlineStr">
+      <c r="A629" s="7" t="inlineStr">
         <is>
           <t>80.10.01</t>
         </is>
       </c>
-      <c r="B629" s="6" t="n"/>
-      <c r="C629" s="6" t="inlineStr">
+      <c r="B629" s="7" t="n"/>
+      <c r="C629" s="7" t="inlineStr">
         <is>
           <t>Din total capitol 80: Actiuni generale economice si comerciale</t>
         </is>
       </c>
-      <c r="D629" s="6" t="n">
+      <c r="D629" s="7" t="n">
         <v>1555</v>
       </c>
-      <c r="E629" s="6" t="n">
+      <c r="E629" s="7" t="n">
         <v>22</v>
       </c>
-      <c r="F629" s="6" t="inlineStr">
+      <c r="F629" s="7" t="inlineStr">
         <is>
           <t>expense_functional</t>
         </is>
       </c>
-      <c r="G629" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H629" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I629" s="7" t="n"/>
-      <c r="J629" s="6" t="inlineStr">
-        <is>
-          <t>digital</t>
-        </is>
-      </c>
-      <c r="K629" s="6" t="inlineStr">
+      <c r="G629" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H629" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I629" s="8" t="n"/>
+      <c r="J629" s="7" t="inlineStr">
+        <is>
+          <t>digital</t>
+        </is>
+      </c>
+      <c r="K629" s="7" t="inlineStr">
         <is>
           <t>duplicate of p10 with different values</t>
         </is>
       </c>
     </row>
     <row r="630">
-      <c r="A630" s="6" t="inlineStr">
+      <c r="A630" s="7" t="inlineStr">
         <is>
           <t>80.10.01.30</t>
         </is>
       </c>
-      <c r="B630" s="6" t="n"/>
-      <c r="C630" s="6" t="inlineStr">
+      <c r="B630" s="7" t="n"/>
+      <c r="C630" s="7" t="inlineStr">
         <is>
           <t>Alte cheltuieli pentru actiuni generale economice si comerciale</t>
         </is>
       </c>
-      <c r="D630" s="6" t="n">
+      <c r="D630" s="7" t="n">
         <v>1556</v>
       </c>
-      <c r="E630" s="6" t="n">
+      <c r="E630" s="7" t="n">
         <v>22</v>
       </c>
-      <c r="F630" s="6" t="inlineStr">
+      <c r="F630" s="7" t="inlineStr">
         <is>
           <t>expense_functional</t>
         </is>
       </c>
-      <c r="G630" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H630" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I630" s="7" t="n"/>
-      <c r="J630" s="6" t="inlineStr">
-        <is>
-          <t>digital</t>
-        </is>
-      </c>
-      <c r="K630" s="6" t="inlineStr">
+      <c r="G630" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H630" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I630" s="8" t="n"/>
+      <c r="J630" s="7" t="inlineStr">
+        <is>
+          <t>digital</t>
+        </is>
+      </c>
+      <c r="K630" s="7" t="inlineStr">
         <is>
           <t>duplicate of p10 with different values</t>
         </is>
       </c>
     </row>
     <row r="631">
-      <c r="A631" s="6" t="inlineStr">
+      <c r="A631" s="7" t="inlineStr">
         <is>
           <t>87.10</t>
         </is>
       </c>
-      <c r="B631" s="6" t="n"/>
-      <c r="C631" s="6" t="inlineStr">
+      <c r="B631" s="7" t="n"/>
+      <c r="C631" s="7" t="inlineStr">
         <is>
           <t>CAP. Alte actiuni economice</t>
         </is>
       </c>
-      <c r="D631" s="6" t="n">
+      <c r="D631" s="7" t="n">
         <v>1595</v>
       </c>
-      <c r="E631" s="6" t="n">
+      <c r="E631" s="7" t="n">
         <v>22</v>
       </c>
-      <c r="F631" s="6" t="inlineStr">
+      <c r="F631" s="7" t="inlineStr">
         <is>
           <t>expense_functional</t>
         </is>
       </c>
-      <c r="G631" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H631" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I631" s="7" t="n"/>
-      <c r="J631" s="6" t="inlineStr">
-        <is>
-          <t>digital</t>
-        </is>
-      </c>
-      <c r="K631" s="6" t="inlineStr">
+      <c r="G631" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H631" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I631" s="8" t="n"/>
+      <c r="J631" s="7" t="inlineStr">
+        <is>
+          <t>digital</t>
+        </is>
+      </c>
+      <c r="K631" s="7" t="inlineStr">
         <is>
           <t>duplicate of p10 with different values</t>
         </is>
       </c>
     </row>
     <row r="632">
-      <c r="A632" s="6" t="inlineStr">
+      <c r="A632" s="7" t="inlineStr">
         <is>
           <t>70</t>
         </is>
       </c>
-      <c r="B632" s="6" t="inlineStr">
+      <c r="B632" s="7" t="inlineStr">
         <is>
           <t>87.10</t>
         </is>
       </c>
-      <c r="C632" s="6" t="inlineStr">
+      <c r="C632" s="7" t="inlineStr">
         <is>
           <t>CHELTUIELI DE CAPITAL</t>
         </is>
       </c>
-      <c r="D632" s="6" t="n">
+      <c r="D632" s="7" t="n">
         <v>1603</v>
       </c>
-      <c r="E632" s="6" t="n">
+      <c r="E632" s="7" t="n">
         <v>22</v>
       </c>
-      <c r="F632" s="6" t="inlineStr">
-        <is>
-          <t>expense_economic</t>
-        </is>
-      </c>
-      <c r="G632" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H632" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I632" s="7" t="n"/>
-      <c r="J632" s="6" t="inlineStr">
-        <is>
-          <t>digital</t>
-        </is>
-      </c>
-      <c r="K632" s="6" t="inlineStr">
+      <c r="F632" s="7" t="inlineStr">
+        <is>
+          <t>expense_economic</t>
+        </is>
+      </c>
+      <c r="G632" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H632" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I632" s="8" t="n"/>
+      <c r="J632" s="7" t="inlineStr">
+        <is>
+          <t>digital</t>
+        </is>
+      </c>
+      <c r="K632" s="7" t="inlineStr">
         <is>
           <t>duplicate of p11 with different values</t>
         </is>
       </c>
     </row>
     <row r="633">
-      <c r="A633" s="6" t="inlineStr">
+      <c r="A633" s="7" t="inlineStr">
         <is>
           <t>71</t>
         </is>
       </c>
-      <c r="B633" s="6" t="inlineStr">
+      <c r="B633" s="7" t="inlineStr">
         <is>
           <t>87.10</t>
         </is>
       </c>
-      <c r="C633" s="6" t="inlineStr">
+      <c r="C633" s="7" t="inlineStr">
         <is>
           <t>TITLUL XV ACTIVE NEFINANCIARE</t>
         </is>
       </c>
-      <c r="D633" s="6" t="n">
+      <c r="D633" s="7" t="n">
         <v>1604</v>
       </c>
-      <c r="E633" s="6" t="n">
+      <c r="E633" s="7" t="n">
         <v>22</v>
       </c>
-      <c r="F633" s="6" t="inlineStr">
-        <is>
-          <t>expense_economic</t>
-        </is>
-      </c>
-      <c r="G633" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H633" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I633" s="7" t="n"/>
-      <c r="J633" s="6" t="inlineStr">
-        <is>
-          <t>digital</t>
-        </is>
-      </c>
-      <c r="K633" s="6" t="inlineStr">
+      <c r="F633" s="7" t="inlineStr">
+        <is>
+          <t>expense_economic</t>
+        </is>
+      </c>
+      <c r="G633" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H633" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I633" s="8" t="n"/>
+      <c r="J633" s="7" t="inlineStr">
+        <is>
+          <t>digital</t>
+        </is>
+      </c>
+      <c r="K633" s="7" t="inlineStr">
         <is>
           <t>duplicate of p11 with different values</t>
         </is>
       </c>
     </row>
     <row r="634">
-      <c r="A634" s="6" t="inlineStr">
+      <c r="A634" s="7" t="inlineStr">
         <is>
           <t>71.01</t>
         </is>
       </c>
-      <c r="B634" s="6" t="inlineStr">
+      <c r="B634" s="7" t="inlineStr">
         <is>
           <t>87.10</t>
         </is>
       </c>
-      <c r="C634" s="6" t="inlineStr">
+      <c r="C634" s="7" t="inlineStr">
         <is>
           <t>Active fixe (cod 71.01.01 la 71.01.03+71.01.30)</t>
         </is>
       </c>
-      <c r="D634" s="6" t="n">
+      <c r="D634" s="7" t="n">
         <v>1604</v>
       </c>
-      <c r="E634" s="6" t="n">
+      <c r="E634" s="7" t="n">
         <v>22</v>
       </c>
-      <c r="F634" s="6" t="inlineStr">
-        <is>
-          <t>expense_economic</t>
-        </is>
-      </c>
-      <c r="G634" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H634" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I634" s="7" t="n"/>
-      <c r="J634" s="6" t="inlineStr">
-        <is>
-          <t>digital</t>
-        </is>
-      </c>
-      <c r="K634" s="6" t="inlineStr">
+      <c r="F634" s="7" t="inlineStr">
+        <is>
+          <t>expense_economic</t>
+        </is>
+      </c>
+      <c r="G634" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H634" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I634" s="8" t="n"/>
+      <c r="J634" s="7" t="inlineStr">
+        <is>
+          <t>digital</t>
+        </is>
+      </c>
+      <c r="K634" s="7" t="inlineStr">
         <is>
           <t>duplicate of p11 with different values</t>
         </is>
       </c>
     </row>
     <row r="635">
-      <c r="A635" s="6" t="inlineStr">
+      <c r="A635" s="7" t="inlineStr">
         <is>
           <t>71.01.02</t>
         </is>
       </c>
-      <c r="B635" s="6" t="inlineStr">
+      <c r="B635" s="7" t="inlineStr">
         <is>
           <t>87.10</t>
         </is>
       </c>
-      <c r="C635" s="6" t="inlineStr">
+      <c r="C635" s="7" t="inlineStr">
         <is>
           <t>Masini, echipamente si mijloace de transport</t>
         </is>
       </c>
-      <c r="D635" s="6" t="n">
+      <c r="D635" s="7" t="n">
         <v>1604</v>
       </c>
-      <c r="E635" s="6" t="n">
+      <c r="E635" s="7" t="n">
         <v>22</v>
       </c>
-      <c r="F635" s="6" t="inlineStr">
-        <is>
-          <t>expense_economic</t>
-        </is>
-      </c>
-      <c r="G635" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H635" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I635" s="7" t="n"/>
-      <c r="J635" s="6" t="inlineStr">
-        <is>
-          <t>digital</t>
-        </is>
-      </c>
-      <c r="K635" s="6" t="inlineStr">
+      <c r="F635" s="7" t="inlineStr">
+        <is>
+          <t>expense_economic</t>
+        </is>
+      </c>
+      <c r="G635" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H635" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I635" s="8" t="n"/>
+      <c r="J635" s="7" t="inlineStr">
+        <is>
+          <t>digital</t>
+        </is>
+      </c>
+      <c r="K635" s="7" t="inlineStr">
         <is>
           <t>duplicate of p11 with different values</t>
         </is>
@@ -25025,123 +25041,123 @@
       </c>
     </row>
     <row r="637">
-      <c r="A637" s="6" t="inlineStr">
+      <c r="A637" s="7" t="inlineStr">
         <is>
           <t>87.10.50</t>
         </is>
       </c>
-      <c r="B637" s="6" t="n"/>
-      <c r="C637" s="6" t="inlineStr">
+      <c r="B637" s="7" t="n"/>
+      <c r="C637" s="7" t="inlineStr">
         <is>
           <t>Din total capitol 87: Alte actiuni economice</t>
         </is>
       </c>
-      <c r="D637" s="6" t="n">
+      <c r="D637" s="7" t="n">
         <v>1611</v>
       </c>
-      <c r="E637" s="6" t="n">
+      <c r="E637" s="7" t="n">
         <v>22</v>
       </c>
-      <c r="F637" s="6" t="inlineStr">
+      <c r="F637" s="7" t="inlineStr">
         <is>
           <t>expense_functional</t>
         </is>
       </c>
-      <c r="G637" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H637" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I637" s="7" t="n"/>
-      <c r="J637" s="6" t="inlineStr">
-        <is>
-          <t>digital</t>
-        </is>
-      </c>
-      <c r="K637" s="6" t="inlineStr">
+      <c r="G637" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H637" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I637" s="8" t="n"/>
+      <c r="J637" s="7" t="inlineStr">
+        <is>
+          <t>digital</t>
+        </is>
+      </c>
+      <c r="K637" s="7" t="inlineStr">
         <is>
           <t>duplicate of p11 with different values</t>
         </is>
       </c>
     </row>
     <row r="638">
-      <c r="A638" s="6" t="inlineStr">
+      <c r="A638" s="7" t="inlineStr">
         <is>
           <t>96.10</t>
         </is>
       </c>
-      <c r="B638" s="6" t="n"/>
-      <c r="C638" s="6" t="inlineStr">
+      <c r="B638" s="7" t="n"/>
+      <c r="C638" s="7" t="inlineStr">
         <is>
           <t>Partea a VII-a REZERVE, EXCEDENT / DEFICIT</t>
         </is>
       </c>
-      <c r="D638" s="6" t="n">
+      <c r="D638" s="7" t="n">
         <v>1612</v>
       </c>
-      <c r="E638" s="6" t="n">
+      <c r="E638" s="7" t="n">
         <v>22</v>
       </c>
-      <c r="F638" s="6" t="inlineStr">
+      <c r="F638" s="7" t="inlineStr">
         <is>
           <t>expense_functional</t>
         </is>
       </c>
-      <c r="G638" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H638" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I638" s="7" t="n"/>
-      <c r="J638" s="6" t="inlineStr">
-        <is>
-          <t>digital</t>
-        </is>
-      </c>
-      <c r="K638" s="6" t="inlineStr">
+      <c r="G638" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H638" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I638" s="8" t="n"/>
+      <c r="J638" s="7" t="inlineStr">
+        <is>
+          <t>digital</t>
+        </is>
+      </c>
+      <c r="K638" s="7" t="inlineStr">
         <is>
           <t>duplicate of p11 with different values</t>
         </is>
       </c>
     </row>
     <row r="639">
-      <c r="A639" s="6" t="inlineStr">
+      <c r="A639" s="7" t="inlineStr">
         <is>
           <t>98.10</t>
         </is>
       </c>
-      <c r="B639" s="6" t="n"/>
-      <c r="C639" s="6" t="inlineStr">
+      <c r="B639" s="7" t="n"/>
+      <c r="C639" s="7" t="inlineStr">
         <is>
           <t>EXCEDENT</t>
         </is>
       </c>
-      <c r="D639" s="6" t="n">
+      <c r="D639" s="7" t="n">
         <v>1614</v>
       </c>
-      <c r="E639" s="6" t="n">
+      <c r="E639" s="7" t="n">
         <v>22</v>
       </c>
-      <c r="F639" s="6" t="inlineStr">
+      <c r="F639" s="7" t="inlineStr">
         <is>
           <t>expense_functional</t>
         </is>
       </c>
-      <c r="G639" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H639" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I639" s="7" t="n"/>
-      <c r="J639" s="6" t="inlineStr">
-        <is>
-          <t>digital</t>
-        </is>
-      </c>
-      <c r="K639" s="6" t="inlineStr">
+      <c r="G639" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H639" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I639" s="8" t="n"/>
+      <c r="J639" s="7" t="inlineStr">
+        <is>
+          <t>digital</t>
+        </is>
+      </c>
+      <c r="K639" s="7" t="inlineStr">
         <is>
           <t>duplicate of p11 with different values</t>
         </is>
@@ -25183,41 +25199,41 @@
       </c>
     </row>
     <row r="641">
-      <c r="A641" s="6" t="inlineStr">
+      <c r="A641" s="7" t="inlineStr">
         <is>
           <t>99.10</t>
         </is>
       </c>
-      <c r="B641" s="6" t="n"/>
-      <c r="C641" s="6" t="inlineStr">
+      <c r="B641" s="7" t="n"/>
+      <c r="C641" s="7" t="inlineStr">
         <is>
           <t>DEFICIT</t>
         </is>
       </c>
-      <c r="D641" s="6" t="n">
+      <c r="D641" s="7" t="n">
         <v>1616</v>
       </c>
-      <c r="E641" s="6" t="n">
+      <c r="E641" s="7" t="n">
         <v>22</v>
       </c>
-      <c r="F641" s="6" t="inlineStr">
+      <c r="F641" s="7" t="inlineStr">
         <is>
           <t>expense_functional</t>
         </is>
       </c>
-      <c r="G641" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H641" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I641" s="7" t="n"/>
-      <c r="J641" s="6" t="inlineStr">
-        <is>
-          <t>digital</t>
-        </is>
-      </c>
-      <c r="K641" s="6" t="inlineStr">
+      <c r="G641" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H641" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I641" s="8" t="n"/>
+      <c r="J641" s="7" t="inlineStr">
+        <is>
+          <t>digital</t>
+        </is>
+      </c>
+      <c r="K641" s="7" t="inlineStr">
         <is>
           <t>duplicate of p11 with different values</t>
         </is>
@@ -25269,7 +25285,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F52"/>
+  <dimension ref="A1:F48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -25315,12 +25331,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -25333,24 +25349,24 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>est2027</t>
+          <t>est2028</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>LLM re-read 2 rows for 65.10 est2027: still inconsistent — UNRESOLVED</t>
+          <t>65.10 est2028: parent 12.957,00 != sum(children) 41,00 (1 children)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -25363,24 +25379,24 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>est2028</t>
+          <t>est2027</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>LLM re-read 2 rows for 65.10 est2028: still inconsistent — UNRESOLVED</t>
+          <t>65.10 est2027: parent 12.916,00 != sum(children) 41,00 (1 children)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>info</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -25393,24 +25409,24 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>est2027</t>
+          <t>est2028</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>LLM re-read 2 rows for 65.10.04 est2027: sum now consistent — applied</t>
+          <t>65.10.04 est2028: parent 41,00 != sum(children) 149,00 (1 children)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>info</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -25423,33 +25439,28 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>est2028</t>
+          <t>est2027</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>LLM re-read 2 rows for 65.10.04 est2028: sum now consistent — applied</t>
+          <t>65.10.04 est2027: parent 41,00 != sum(children) 149,00 (1 children)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>10</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>87.10</t>
-        </is>
+        <v>6</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -25458,97 +25469,92 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>LLM re-read 2 rows for 87.10 credite_angajament: still inconsistent — UNRESOLVED</t>
+          <t>unparseable cell '0.00 0.00' in column credite_angajament</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>87.10</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>est2027</t>
+          <t>credite_angajament</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>LLM re-read 4 rows for 10 est2027: still inconsistent — UNRESOLVED</t>
+          <t>87.10 credite_angajament: parent 0,00 != sum(children) 7,00 (1 children)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>87.10</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>est2028</t>
+          <t>credite_angajament</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>LLM re-read 4 rows for 10 est2028: still inconsistent — UNRESOLVED</t>
+          <t>87.10 credite_angajament: parent 0,00 != sum(children) 7,00 (2 children)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>V4_hierarchy</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V2_name</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>65.10</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>est2028</t>
+          <t>33.10.08</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>65.10 est2028: parent 12.957,00 != sum(children) 41,00 (1 children)</t>
+          <t>name mismatch vs nomenclator (2%): '331005+331008+331013+331014+331016+33101' vs 'Venituri din prestari de servicii'</t>
         </is>
       </c>
     </row>
@@ -25564,21 +25570,21 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>65.10</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>est2027</t>
+          <t>est2028</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>65.10 est2027: parent 12.916,00 != sum(children) 41,00 (1 children)</t>
+          <t>10 est2028: parent 84.448,00 != sum(children) 267.882,00 (3 children)</t>
         </is>
       </c>
     </row>
@@ -25594,58 +25600,53 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>87.10</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>credite_angajament</t>
+          <t>est2027</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>87.10 credite_angajament: parent 0,00 != sum(children) 7,00 (1 children)</t>
+          <t>10 est2027: parent 84.283,00 != sum(children) 267.152,00 (3 children)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>V4_hierarchy</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>87.10</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>credite_angajament</t>
+          <t>10.01</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>87.10 credite_angajament: parent 0,00 != sum(children) 7,00 (2 children)</t>
+          <t>duplicate of p12 with different values</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>V2_name</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -25654,76 +25655,66 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>33.10.08</t>
+          <t>43.10.19</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (2%): '331005+331008+331013+331014+331016+33101' vs 'Venituri din prestari de servicii'</t>
+          <t>duplicate of p2 with different values</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>V4_hierarchy</t>
-        </is>
-      </c>
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>est2028</t>
+          <t>50.10</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>10 est2028: parent 84.448,00 != sum(children) 267.882,00 (3 children)</t>
+          <t>duplicate of p2 with different values</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>V4_hierarchy</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>est2027</t>
+          <t>70</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>10 est2027: parent 84.283,00 != sum(children) 267.152,00 (3 children)</t>
+          <t>duplicate of p4 with different values</t>
         </is>
       </c>
     </row>
@@ -25739,16 +25730,16 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>10.01</t>
+          <t>71</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>duplicate of p12 with different values</t>
+          <t>duplicate of p4 with different values</t>
         </is>
       </c>
     </row>
@@ -25768,12 +25759,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>43.10.19</t>
+          <t>71.01</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>duplicate of p2 with different values</t>
+          <t>duplicate of p4 with different values</t>
         </is>
       </c>
     </row>
@@ -25793,12 +25784,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>50.10</t>
+          <t>71.01.01</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>duplicate of p2 with different values</t>
+          <t>duplicate of p4 with different values</t>
         </is>
       </c>
     </row>
@@ -25818,7 +25809,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>71.01.02</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -25843,7 +25834,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>71.01.30</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -25868,7 +25859,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>71.01</t>
+          <t>54.10</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -25893,12 +25884,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>71.01.01</t>
+          <t>70</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>duplicate of p4 with different values</t>
+          <t>duplicate of p5 with different values</t>
         </is>
       </c>
     </row>
@@ -25918,12 +25909,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>71.01.02</t>
+          <t>71</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>duplicate of p4 with different values</t>
+          <t>duplicate of p5 with different values</t>
         </is>
       </c>
     </row>
@@ -25943,12 +25934,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>71.01.30</t>
+          <t>71.01</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>duplicate of p4 with different values</t>
+          <t>duplicate of p5 with different values</t>
         </is>
       </c>
     </row>
@@ -25968,12 +25959,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>54.10</t>
+          <t>71.01.02</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>duplicate of p4 with different values</t>
+          <t>duplicate of p5 with different values</t>
         </is>
       </c>
     </row>
@@ -25993,7 +25984,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>54.10.10</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -26018,7 +26009,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>59.10</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -26043,7 +26034,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>71.01</t>
+          <t>63.10</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -26068,12 +26059,12 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>71.01.02</t>
+          <t>67.10</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>duplicate of p5 with different values</t>
+          <t>duplicate of p6 with different values</t>
         </is>
       </c>
     </row>
@@ -26093,12 +26084,12 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>54.10.10</t>
+          <t>70</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>duplicate of p5 with different values</t>
+          <t>duplicate of p8 with different values</t>
         </is>
       </c>
     </row>
@@ -26118,12 +26109,12 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>59.10</t>
+          <t>71</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>duplicate of p5 with different values</t>
+          <t>duplicate of p8 with different values</t>
         </is>
       </c>
     </row>
@@ -26143,12 +26134,12 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>63.10</t>
+          <t>71.01</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>duplicate of p5 with different values</t>
+          <t>duplicate of p8 with different values</t>
         </is>
       </c>
     </row>
@@ -26164,16 +26155,16 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>67.10</t>
+          <t>67.10.03</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>duplicate of p6 with different values</t>
+          <t>duplicate of p9 with different values</t>
         </is>
       </c>
     </row>
@@ -26189,16 +26180,16 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>67.10.03.04</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>duplicate of p8 with different values</t>
+          <t>duplicate of p9 with different values</t>
         </is>
       </c>
     </row>
@@ -26214,16 +26205,16 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>67.10.03.30</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>duplicate of p8 with different values</t>
+          <t>duplicate of p9 with different values</t>
         </is>
       </c>
     </row>
@@ -26239,16 +26230,16 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>71.01</t>
+          <t>79.10</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>duplicate of p8 with different values</t>
+          <t>duplicate of p9 with different values</t>
         </is>
       </c>
     </row>
@@ -26268,7 +26259,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>67.10.03</t>
+          <t>80.10</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -26293,12 +26284,12 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>67.10.03.04</t>
+          <t>80.10.01</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>duplicate of p9 with different values</t>
+          <t>duplicate of p10 with different values</t>
         </is>
       </c>
     </row>
@@ -26318,12 +26309,12 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>67.10.03.30</t>
+          <t>80.10.01.30</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>duplicate of p9 with different values</t>
+          <t>duplicate of p10 with different values</t>
         </is>
       </c>
     </row>
@@ -26343,12 +26334,12 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>79.10</t>
+          <t>87.10</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>duplicate of p9 with different values</t>
+          <t>duplicate of p10 with different values</t>
         </is>
       </c>
     </row>
@@ -26368,12 +26359,12 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>80.10</t>
+          <t>70</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>duplicate of p9 with different values</t>
+          <t>duplicate of p11 with different values</t>
         </is>
       </c>
     </row>
@@ -26393,12 +26384,12 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>80.10.01</t>
+          <t>71</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>duplicate of p10 with different values</t>
+          <t>duplicate of p11 with different values</t>
         </is>
       </c>
     </row>
@@ -26418,12 +26409,12 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>80.10.01.30</t>
+          <t>71.01</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>duplicate of p10 with different values</t>
+          <t>duplicate of p11 with different values</t>
         </is>
       </c>
     </row>
@@ -26443,12 +26434,12 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>87.10</t>
+          <t>71.01.02</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>duplicate of p10 with different values</t>
+          <t>duplicate of p11 with different values</t>
         </is>
       </c>
     </row>
@@ -26468,7 +26459,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>87.10.50</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -26493,7 +26484,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>96.10</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -26518,7 +26509,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>71.01</t>
+          <t>98.10</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -26543,110 +26534,10 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>71.01.02</t>
+          <t>99.10</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
-        <is>
-          <t>duplicate of p11 with different values</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="C49" t="n">
-        <v>22</v>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>87.10.50</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>duplicate of p11 with different values</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="C50" t="n">
-        <v>22</v>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>96.10</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>duplicate of p11 with different values</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="C51" t="n">
-        <v>22</v>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>98.10</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>duplicate of p11 with different values</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="C52" t="n">
-        <v>22</v>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>99.10</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
         <is>
           <t>duplicate of p11 with different values</t>
         </is>
@@ -26663,7 +26554,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -26685,7 +26576,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Documente</t>
+          <t>Schema calitate</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -26695,72 +26586,230 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Linii de date</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>614</v>
+          <t>Metrica de calitate</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>observed_strict_line_rate</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Linii fara probleme</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>573</v>
+          <t>Recall masurat</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>nu</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>% curat</t>
+          <t>Documente</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>93.3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Erori</t>
+          <t>Linii de date</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6</v>
+        <v>614</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Avertismente</t>
+          <t>Linii strict verificate</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>43</v>
+        <v>572</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Modele LLM folosite</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>gemini-3.6-flash</t>
-        </is>
+          <t>% linii strict verificate</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>93.2</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
+          <t>Celule numerice</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1402</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Celule numerice strict verificate</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1294</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>% celule numerice strict verificate</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>92.3</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Pagini asteptate</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Pagini selectate</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Pagini procesate</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>PDF complet</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>da</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Linii fara probleme</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>% curat</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>93.2</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Erori</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>Avertismente</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>Informatii</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>Schema publicare</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>Bundle conversie</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>1ad6c514671f84a3810cf9b5</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>SHA-256 PDF sursa</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>8d78930d79aacba6f83c416a78314f0e02a771aa886d0e9625e903f66d2ec40a</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
           <t>— BUGETUL CENTRALIZAT AL INSTITUTIILOR PUBLICE SI ACTIVITATILO</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>own_revenue, pag. 1-23, 647 linii</t>
         </is>
